--- a/produits/preuves/sortie/si-et/si-et.xlsx
+++ b/produits/preuves/sortie/si-et/si-et.xlsx
@@ -263,9 +263,11 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
